--- a/order_forms/041_e_commerce_platform_integration_order_form--order_forms.xlsx
+++ b/order_forms/041_e_commerce_platform_integration_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>api_credentials</t>
+          <t>api_credentials_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>API Credentials</t>
+          <t>Api Credentials 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>store_url</t>
+          <t>store_url_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Store URL</t>
+          <t>Store Url 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>order_status</t>
+          <t>order_status_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Order Status 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>integration_type</t>
+          <t>integration_type_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Integration Type</t>
+          <t>Integration Type 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'shopify'}</t>
+          <t>shopify</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Shopify'}</t>
+          <t>Shopify</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'woocommerce'}</t>
+          <t>woocommerce</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Woocommerce'}</t>
+          <t>Woocommerce</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'bigcommerce'}</t>
+          <t>bigcommerce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'BigCommerce'}</t>
+          <t>BigCommerce</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'api'}</t>
+          <t>api</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'API'}</t>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'api'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'API'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>integration_method_choices</t>
+          <t>integration_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'api'}</t>
+          <t>full_integration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'API'}</t>
+          <t>Full Integration</t>
         </is>
       </c>
     </row>
@@ -1233,46 +1233,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'full_integration'}</t>
+          <t>partial_integration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Full Integration'}</t>
+          <t>Partial Integration</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>order_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'partial_integration'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Partial Integration'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>order_status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'full_integration'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Full Integration'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1284,46 +1284,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'new'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'New'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'pending'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Pending'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'cancelled'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Cancelled'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1335,46 +1335,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'card'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Card'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>store_language_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'paypal'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'PayPal'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>store_language_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'bank'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Bank'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1386,199 +1386,148 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'english'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'English'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>store_language_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'spanish'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Spanish'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>store_language_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'french'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'French'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'new'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'New'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>integration_type_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'pending'}</t>
+          <t>full_integration</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Pending'}</t>
+          <t>Full Integration</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>integration_type_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'cancelled'}</t>
+          <t>partial_integration</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Cancelled'}</t>
+          <t>Partial Integration</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'full_integration'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Full Integration'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'partial_integration'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Partial Integration'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'full_integration'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Full Integration'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'id':_'1',_'label':_'card'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'id': '1', 'label': 'Card'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'id':_'2',_'label':_'paypal'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'id': '2', 'label': 'PayPal'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'id':_'3',_'label':_'bank'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'id': '3', 'label': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
